--- a/svaproy_export_tmp.xlsx
+++ b/svaproy_export_tmp.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
-  <si>
-    <t>72986227</t>
-  </si>
-  <si>
-    <t>NICOLAS JEREMY JULIAN, GONZA|MARTINEZ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="22">
+  <si>
+    <t>72983782</t>
+  </si>
+  <si>
+    <t>ADRIANO SEBASTIAN, ESPINOZA|PALACIOS</t>
   </si>
   <si>
     <t>202610</t>
@@ -26,16 +26,16 @@
     <t/>
   </si>
   <si>
-    <t>PR01PSIC</t>
-  </si>
-  <si>
-    <t>INVE</t>
-  </si>
-  <si>
-    <t>01010</t>
-  </si>
-  <si>
-    <t>RAZ. LOGICO MATEMÁTICO</t>
+    <t>PR02ISIA</t>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
+    <t>02001</t>
+  </si>
+  <si>
+    <t>INTRO. A LA COMPUTACIÓN</t>
   </si>
   <si>
     <t>PR</t>
@@ -50,25 +50,34 @@
     <t>PEDROROTTA</t>
   </si>
   <si>
-    <t>PSFU</t>
-  </si>
-  <si>
-    <t>01002</t>
-  </si>
-  <si>
-    <t>P. OBSERVACIÓN Y ENTREVISTA</t>
-  </si>
-  <si>
-    <t>01001</t>
-  </si>
-  <si>
-    <t>PSI. GENERAL</t>
-  </si>
-  <si>
-    <t>EPSI</t>
-  </si>
-  <si>
-    <t>LPSI</t>
+    <t>MATE</t>
+  </si>
+  <si>
+    <t>02016</t>
+  </si>
+  <si>
+    <t>MATEMÁTICA DISCRETA 1</t>
+  </si>
+  <si>
+    <t>02008</t>
+  </si>
+  <si>
+    <t>GEOMET. ANALÍTICA VECTORIAL</t>
+  </si>
+  <si>
+    <t>02006</t>
+  </si>
+  <si>
+    <t>CÁLCULO ELEMENTAL</t>
+  </si>
+  <si>
+    <t>ESTU</t>
+  </si>
+  <si>
+    <t>ORIENTACIÓN UNIVERSITARIA</t>
+  </si>
+  <si>
+    <t>EISI</t>
   </si>
 </sst>
 </file>
@@ -120,11 +129,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.8125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.8203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.71875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="7.60546875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="2.0859375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="0.984375" customWidth="true" bestFit="true"/>
@@ -174,10 +183,10 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="J2" t="s">
         <v>9</v>
@@ -192,7 +201,7 @@
         <v>11</v>
       </c>
       <c r="N2" t="n" s="2">
-        <v>46156.03703703704</v>
+        <v>46156.45920138889</v>
       </c>
     </row>
     <row r="3">
@@ -218,10 +227,10 @@
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="J3" t="s">
         <v>9</v>
@@ -236,7 +245,7 @@
         <v>11</v>
       </c>
       <c r="N3" t="n" s="2">
-        <v>46156.03703703704</v>
+        <v>46156.45920138889</v>
       </c>
     </row>
     <row r="4">
@@ -262,10 +271,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="J4" t="s">
         <v>9</v>
@@ -280,7 +289,7 @@
         <v>11</v>
       </c>
       <c r="N4" t="n" s="2">
-        <v>46156.03703703704</v>
+        <v>46156.45920138889</v>
       </c>
     </row>
     <row r="5">
@@ -291,29 +300,31 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>70.0</v>
-      </c>
-      <c r="I5"/>
+        <v>30.0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.0</v>
+      </c>
       <c r="J5" t="s">
         <v>9</v>
       </c>
       <c r="K5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L5" t="s">
         <v>3</v>
@@ -322,7 +333,7 @@
         <v>11</v>
       </c>
       <c r="N5" t="n" s="2">
-        <v>46156.03703703704</v>
+        <v>46156.45920138889</v>
       </c>
     </row>
     <row r="6">
@@ -333,38 +344,82 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n" s="2">
+        <v>46156.45920138889</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="n">
         <v>90.0</v>
       </c>
-      <c r="I6"/>
-      <c r="J6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" t="s">
-        <v>11</v>
-      </c>
-      <c r="N6" t="n" s="2">
-        <v>46156.03703703704</v>
+      <c r="I7"/>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" t="n" s="2">
+        <v>46156.45920138889</v>
       </c>
     </row>
   </sheetData>
